--- a/TestData/SigninInput.xlsx
+++ b/TestData/SigninInput.xlsx
@@ -393,6 +393,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
